--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2018_metropolitana.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2018_metropolitana.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 13:36</t>
+    <t xml:space="preserve">2026-09-09 19:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2018_metropolitana.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2018_metropolitana.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:54</t>
+    <t xml:space="preserve">2026-09-18 17:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2018_metropolitana.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2018_metropolitana.xlsx
@@ -8,20 +8,19 @@
   <sheets>
     <sheet name="Total_Regional" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Por_Sexo" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Por_Prov" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Por_Edad" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Regiones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Por_Edad" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Por_Edad'!$A$1:$E$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Por_Edad'!$A$1:$E$18</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
-  <si>
-    <t xml:space="preserve">Categoria</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+  <si>
+    <t xml:space="preserve">region</t>
   </si>
   <si>
     <t xml:space="preserve">Residentes</t>
@@ -33,10 +32,7 @@
     <t xml:space="preserve">Cobertura</t>
   </si>
   <si>
-    <t xml:space="preserve">Categoria_lbl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total</t>
+    <t xml:space="preserve">Metropolitana</t>
   </si>
   <si>
     <t xml:space="preserve">Campo</t>
@@ -48,7 +44,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 17:02</t>
+    <t xml:space="preserve">2026-09-27 21:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -81,91 +77,100 @@
     <t xml:space="preserve">2018</t>
   </si>
   <si>
-    <t xml:space="preserve">region</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sexo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metropolitana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Masculino</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Femenino</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Provincia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melipilla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chacabuco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talagante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maipo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cordillera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santiago</t>
+    <t xml:space="preserve">Tarapacá</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Lagos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aysén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magallanes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Ríos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arica y Parinacota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ñuble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antofagasta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atacama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coquimbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valparaíso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O'Higgins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biobío</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Araucanía</t>
   </si>
   <si>
     <t xml:space="preserve">Tramo_Edad</t>
   </si>
   <si>
-    <t xml:space="preserve">0-4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5-9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30-34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40-44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45-49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50-54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55-59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60-64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65-69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70-74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75-79</t>
+    <t xml:space="preserve">0–4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5–9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10–14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15–19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20–24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25–29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30–34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35–39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40–44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45–49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50–54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55–59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60–64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65–69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70–74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75–79</t>
   </si>
   <si>
     <t xml:space="preserve">80+</t>
@@ -533,11 +538,10 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="11.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="15.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="12.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="15.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -553,13 +557,10 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>7287472</v>
@@ -570,12 +571,9 @@
       <c r="D2" s="2" t="n">
         <v>94.61</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>5</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E2"/>
+  <autoFilter ref="A1:D2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -592,58 +590,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -657,66 +655,252 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="15.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="20.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="12.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>346319</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3551641</v>
+        <v>354940</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>3793180</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>93.63</v>
+        <v>97.57</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>872676</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>877348</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>99.47</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>109305</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>106023</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>103.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B5" s="2" t="n">
+        <v>169825</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>173567</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>97.84</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>7287472</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>7702891</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>94.61</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>393004</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>400935</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>98.02</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>3735831</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>3909711</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>95.55</v>
+      <c r="B8" s="2" t="n">
+        <v>239581</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>241901</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>99.04</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>520822</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>504248</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>103.29</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>631096</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>645022</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>97.84</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>312296</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>307835</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>101.45</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>785802</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>807213</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>97.35</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>1846461</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>1910385</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>96.65</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>953750</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>966486</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>98.68</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>1082259</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>1105731</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>97.88</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>1575534</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>1645460</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>95.75</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>996078</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>1001420</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>99.47</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E3"/>
+  <autoFilter ref="A1:D17"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -736,10 +920,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -753,233 +937,95 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>194478</v>
+        <v>424881</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>203925</v>
+        <v>501835</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>95.37</v>
+        <v>84.67</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>263110</v>
+        <v>465906</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>299498</v>
+        <v>500511</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>87.85</v>
+        <v>93.09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>309735</v>
+        <v>447007</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>323234</v>
+        <v>468236</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>95.82</v>
+        <v>95.47</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>510336</v>
+        <v>485017</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>533712</v>
+        <v>509554</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>95.62</v>
+        <v>95.18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>618809</v>
+        <v>578443</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>662253</v>
+        <v>629400</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>93.44</v>
+        <v>91.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>5391004</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>5680269</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>94.91</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E7"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="15.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="12.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>424881</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>501835</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>84.67</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>465906</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>500511</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>93.09</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>447007</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>468236</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>95.47</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>485017</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>509554</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>95.18</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>578443</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>629400</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>91.9</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>678580</v>
@@ -993,10 +1039,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>609335</v>
@@ -1010,10 +1056,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>550767</v>
@@ -1027,10 +1073,10 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>494512</v>
@@ -1044,10 +1090,10 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>477687</v>
@@ -1061,10 +1107,10 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>470771</v>
@@ -1078,10 +1124,10 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>437992</v>
@@ -1095,10 +1141,10 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>347334</v>
@@ -1112,10 +1158,10 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>266186</v>
@@ -1129,10 +1175,10 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>212681</v>
@@ -1146,10 +1192,10 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>149069</v>
@@ -1163,10 +1209,10 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>191304</v>

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2018_metropolitana.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2018_metropolitana.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 21:44</t>
+    <t xml:space="preserve">2026-10-05 05:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
